--- a/artfynd/A 48581-2020 artfynd.xlsx
+++ b/artfynd/A 48581-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48581-2020 artfynd.xlsx
+++ b/artfynd/A 48581-2020 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120896868</v>
+        <v>120896968</v>
       </c>
       <c r="B3" t="n">
-        <v>91305</v>
+        <v>91089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Runtorp, Runtorp, Sm</t>
+          <t>Runtorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558308</v>
+        <v>558341</v>
       </c>
       <c r="R3" t="n">
-        <v>6274198</v>
+        <v>6274169</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120896968</v>
+        <v>120896868</v>
       </c>
       <c r="B4" t="n">
-        <v>91079</v>
+        <v>91315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,36 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040162</v>
+        <v>6031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Runtorp, Sm</t>
+          <t>Runtorp, Runtorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558341</v>
+        <v>558308</v>
       </c>
       <c r="R4" t="n">
-        <v>6274169</v>
+        <v>6274198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
